--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3203,6 +3203,228 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122999352</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57428</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NV om Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>635870</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6668427</v>
+      </c>
+      <c r="S22" t="n">
+        <v>75</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122999351</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NV om Slätmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>635870</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6668427</v>
+      </c>
+      <c r="S23" t="n">
+        <v>75</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -3205,10 +3205,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122999352</v>
+        <v>122999351</v>
       </c>
       <c r="B22" t="n">
-        <v>57428</v>
+        <v>56688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3243,9 +3243,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122999351</v>
+        <v>122999352</v>
       </c>
       <c r="B23" t="n">
-        <v>56688</v>
+        <v>57428</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3354,9 +3354,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -3205,10 +3205,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122999351</v>
+        <v>122999352</v>
       </c>
       <c r="B22" t="n">
-        <v>56688</v>
+        <v>57428</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3243,9 +3243,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122999352</v>
+        <v>122999351</v>
       </c>
       <c r="B23" t="n">
-        <v>57428</v>
+        <v>56688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3354,9 +3354,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -3205,10 +3205,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122999351</v>
+        <v>122999352</v>
       </c>
       <c r="B22" t="n">
-        <v>56688</v>
+        <v>57431</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3243,9 +3243,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122999352</v>
+        <v>122999351</v>
       </c>
       <c r="B23" t="n">
-        <v>57428</v>
+        <v>56691</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3354,9 +3354,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -3205,10 +3205,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122999352</v>
+        <v>122999351</v>
       </c>
       <c r="B22" t="n">
-        <v>57431</v>
+        <v>56697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3243,9 +3243,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3316,10 +3316,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122999351</v>
+        <v>122999352</v>
       </c>
       <c r="B23" t="n">
-        <v>56691</v>
+        <v>57437</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3332,21 +3332,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3354,9 +3354,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -3319,11 +3319,11 @@
         <v>122999352</v>
       </c>
       <c r="B23" t="n">
-        <v>57437</v>
+        <v>57463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -3319,7 +3319,7 @@
         <v>122999352</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>57480</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -3319,12 +3319,7 @@
         <v>122999352</v>
       </c>
       <c r="B23" t="n">
-        <v>57480</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3420,6 +3420,122 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133505411</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stora harbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>635871</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6668415</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47453-2023 artfynd.xlsx
+++ b/artfynd/A 47453-2023 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68585429</v>
+        <v>68585421</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636076.7520432948</v>
+        <v>635975</v>
       </c>
       <c r="R2" t="n">
-        <v>6667972.30255073</v>
+        <v>6668197</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,21 +743,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>murken granved</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,55 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68585430</v>
+        <v>68585402</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1506</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635990.6200665103</v>
+        <v>635920</v>
       </c>
       <c r="R3" t="n">
-        <v>6667869.851443144</v>
+        <v>6668314</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,21 +850,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -911,7 +871,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,55 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68585442</v>
+        <v>68585440</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636008.6006034913</v>
+        <v>635929</v>
       </c>
       <c r="R4" t="n">
-        <v>6667883.486415255</v>
+        <v>6667887</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,21 +957,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1038,7 +978,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>grov gammal tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68585440</v>
+        <v>68585441</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635928.5496431673</v>
+        <v>635951</v>
       </c>
       <c r="R5" t="n">
-        <v>6667886.505113894</v>
+        <v>6667893</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,19 +1064,9 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-12-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,43 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68585439</v>
+        <v>68585420</v>
       </c>
       <c r="B6" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635851.9440143941</v>
+        <v>635944</v>
       </c>
       <c r="R6" t="n">
-        <v>6668282.174685091</v>
+        <v>6668099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,19 +1186,14 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>stationär i området under hela dagen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,12 +1207,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>äldre blandskog</t>
+          <t>äldre blandskog med gott om döda granar</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>död gran med skalbaggslarver</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,58 +1230,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68585404</v>
+        <v>122999351</v>
       </c>
       <c r="B7" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101520</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större flatbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N om Velången, Upl</t>
+          <t>NV om Slätmossen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635903.614752138</v>
+        <v>635870</v>
       </c>
       <c r="R7" t="n">
-        <v>6668465.123397396</v>
+        <v>6668427</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1380,22 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-12-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-12-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,16 +1320,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre blandskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>björkhögstubbe</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1432,50 +1336,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68585402</v>
+        <v>68585438</v>
       </c>
       <c r="B8" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1506</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635919.7006253203</v>
+        <v>635852</v>
       </c>
       <c r="R8" t="n">
-        <v>6668314.109605129</v>
+        <v>6668282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,21 +1409,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1536,7 +1430,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1554,15 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68585445</v>
+        <v>68585403</v>
       </c>
       <c r="B9" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1599,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635916.3127717759</v>
+        <v>635914</v>
       </c>
       <c r="R9" t="n">
-        <v>6668176.33293742</v>
+        <v>6668438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1632,21 +1521,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1663,7 +1542,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1684,12 +1563,7 @@
         <v>68585418</v>
       </c>
       <c r="B10" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635934.0989800413</v>
+        <v>635934</v>
       </c>
       <c r="R10" t="n">
-        <v>6668006.417087893</v>
+        <v>6668006</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1759,19 +1633,9 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-12-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1808,15 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68585403</v>
+        <v>68585419</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635914.1079302774</v>
+        <v>635969</v>
       </c>
       <c r="R11" t="n">
-        <v>6668438.083245676</v>
+        <v>6668083</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1886,19 +1745,9 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2017-12-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,50 +1784,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68585446</v>
+        <v>68585429</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>635853.3972301218</v>
+        <v>636077</v>
       </c>
       <c r="R12" t="n">
-        <v>6668472.239849364</v>
+        <v>6667972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2008,21 +1857,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2039,7 +1878,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>gammal gran</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2057,50 +1896,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68585441</v>
+        <v>68585430</v>
       </c>
       <c r="B13" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>635950.7986277713</v>
+        <v>635991</v>
       </c>
       <c r="R13" t="n">
-        <v>6667892.816124567</v>
+        <v>6667870</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2130,21 +1969,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2161,7 +1990,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>grov gammal tall</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2179,37 +2008,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68585401</v>
+        <v>68585439</v>
       </c>
       <c r="B14" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101520</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Större flatbagge</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2224,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635972.3594663583</v>
+        <v>635852</v>
       </c>
       <c r="R14" t="n">
-        <v>6668308.580232145</v>
+        <v>6668282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2257,21 +2081,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2288,7 +2102,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>björkhögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2306,15 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>68585438</v>
+        <v>68585442</v>
       </c>
       <c r="B15" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2322,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2351,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635851.9440143941</v>
+        <v>636009</v>
       </c>
       <c r="R15" t="n">
-        <v>6668282.174685091</v>
+        <v>6667883</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2384,19 +2193,9 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2017-12-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2433,50 +2232,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68585421</v>
+        <v>68585444</v>
       </c>
       <c r="B16" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>N om Velången, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>635974.998114306</v>
+        <v>636010</v>
       </c>
       <c r="R16" t="n">
-        <v>6668196.961251317</v>
+        <v>6667950</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2506,21 +2305,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2537,7 +2326,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>murken granved</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2555,15 +2344,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>68585417</v>
+        <v>68585400</v>
       </c>
       <c r="B17" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6275</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>635999.9376032365</v>
+        <v>635968</v>
       </c>
       <c r="R17" t="n">
-        <v>6668009.355946171</v>
+        <v>6668220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2633,21 +2417,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2664,7 +2438,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>död björk</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2682,37 +2456,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68585419</v>
+        <v>68585401</v>
       </c>
       <c r="B18" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>101520</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2727,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635969.229180614</v>
+        <v>635972</v>
       </c>
       <c r="R18" t="n">
-        <v>6668083.032229394</v>
+        <v>6668309</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2760,21 +2529,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2791,7 +2550,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2809,15 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>68585400</v>
+        <v>68585404</v>
       </c>
       <c r="B19" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6275</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2599,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2854,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635967.6633484508</v>
+        <v>635904</v>
       </c>
       <c r="R19" t="n">
-        <v>6668219.631499407</v>
+        <v>6668465</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2887,19 +2641,9 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2017-12-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2936,37 +2680,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>68585444</v>
+        <v>68585417</v>
       </c>
       <c r="B20" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6275</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>101520</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2981,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636010.1176721419</v>
+        <v>636000</v>
       </c>
       <c r="R20" t="n">
-        <v>6667950.379366377</v>
+        <v>6668009</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3014,21 +2753,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3045,7 +2774,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>död björk</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3063,53 +2792,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>68585420</v>
+        <v>68585445</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3118,10 +2832,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635944.1736532878</v>
+        <v>635916</v>
       </c>
       <c r="R21" t="n">
-        <v>6668098.562663951</v>
+        <v>6668176</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3151,26 +2865,11 @@
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2017-12-04</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>stationär i området under hela dagen</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3182,12 +2881,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>äldre blandskog med gott om döda granar</t>
+          <t>äldre blandskog</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>död gran med skalbaggslarver</t>
+          <t>björkhögstubbe</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3205,37 +2904,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122999351</v>
+        <v>122999352</v>
       </c>
       <c r="B22" t="n">
-        <v>56697</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3243,9 +2937,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3316,32 +3010,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122999352</v>
+        <v>133505411</v>
       </c>
       <c r="B23" t="n">
-        <v>57493</v>
+        <v>58136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3349,24 +3043,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NV om Slätmossen, Upl</t>
+          <t>Stora harbacken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635870</v>
+        <v>635871</v>
       </c>
       <c r="R23" t="n">
-        <v>6668427</v>
+        <v>6668415</v>
       </c>
       <c r="S23" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3390,12 +3079,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3410,64 +3114,72 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133505411</v>
+        <v>125708648</v>
       </c>
       <c r="B24" t="n">
-        <v>58136</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stora harbacken, Upl</t>
+          <t>Knärot, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635871</v>
+        <v>635799</v>
       </c>
       <c r="R24" t="n">
-        <v>6668415</v>
+        <v>6667980</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3491,27 +3203,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:10</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3520,18 +3217,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sara Werne</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Sara Werne</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
